--- a/input_data/admin_data/PER/_clean/total-pre-PER.xlsx
+++ b/input_data/admin_data/PER/_clean/total-pre-PER.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="93">
   <si>
     <t>year</t>
   </si>
@@ -24,6 +24,249 @@
   </si>
   <si>
     <t>PER</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>sh_rent</t>
+  </si>
+  <si>
+    <t>sh_capital</t>
+  </si>
+  <si>
+    <t>sh_labour</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>sh_rent</t>
+  </si>
+  <si>
+    <t>sh_capital</t>
+  </si>
+  <si>
+    <t>sh_labour</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>sh_rent</t>
+  </si>
+  <si>
+    <t>sh_capital</t>
+  </si>
+  <si>
+    <t>sh_labour</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t/>
@@ -99,34 +342,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="H1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="I1" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2">
@@ -134,7 +377,7 @@
         <v>2016</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>30866494</v>
@@ -164,7 +407,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C3">
         <v>30866494</v>
@@ -194,7 +437,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <v>30866494</v>
@@ -224,7 +467,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>30866494</v>
@@ -254,7 +497,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>30866494</v>
@@ -284,7 +527,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>30866494</v>
@@ -314,7 +557,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="C8">
         <v>30866494</v>
@@ -344,7 +587,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>30866494</v>
@@ -374,7 +617,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C10">
         <v>30866494</v>
@@ -404,7 +647,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C11">
         <v>30866494</v>
@@ -434,7 +677,7 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C12">
         <v>30866494</v>
@@ -464,7 +707,7 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C13">
         <v>30866494</v>
@@ -494,7 +737,7 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>30866494</v>
@@ -524,7 +767,7 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C15">
         <v>30866494</v>
@@ -554,7 +797,7 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C16">
         <v>30866494</v>
@@ -584,7 +827,7 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C17">
         <v>30866494</v>
@@ -614,7 +857,7 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C18">
         <v>30866494</v>
@@ -652,34 +895,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="H1" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="I1" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2">
@@ -687,7 +930,7 @@
         <v>2017</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="C2">
         <v>31324636</v>
@@ -717,7 +960,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="C3">
         <v>31324636</v>
@@ -747,7 +990,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="C4">
         <v>31324636</v>
@@ -777,7 +1020,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C5">
         <v>31324636</v>
@@ -807,7 +1050,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="C6">
         <v>31324636</v>
@@ -837,7 +1080,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="C7">
         <v>31324636</v>
@@ -867,7 +1110,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="C8">
         <v>31324636</v>
@@ -897,7 +1140,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C9">
         <v>31324636</v>
@@ -927,7 +1170,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="C10">
         <v>31324636</v>
@@ -957,7 +1200,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="C11">
         <v>31324636</v>
@@ -987,7 +1230,7 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="C12">
         <v>31324636</v>
@@ -1017,7 +1260,7 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C13">
         <v>31324636</v>
@@ -1047,7 +1290,7 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="C14">
         <v>31324636</v>
@@ -1077,7 +1320,7 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C15">
         <v>31324636</v>
@@ -1107,7 +1350,7 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C16">
         <v>31324636</v>
@@ -1137,7 +1380,7 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C17">
         <v>31324636</v>
@@ -1167,7 +1410,7 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="C18">
         <v>31324636</v>
@@ -1205,34 +1448,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="H1" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
@@ -1240,7 +1483,7 @@
         <v>2018</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="C2">
         <v>31897584</v>
@@ -1270,7 +1513,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="C3">
         <v>31897584</v>
@@ -1300,7 +1543,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>70</v>
       </c>
       <c r="C4">
         <v>31897584</v>
@@ -1330,7 +1573,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C5">
         <v>31897584</v>
@@ -1360,7 +1603,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="C6">
         <v>31897584</v>
@@ -1390,7 +1633,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="C7">
         <v>31897584</v>
@@ -1420,7 +1663,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="C8">
         <v>31897584</v>
@@ -1450,7 +1693,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="C9">
         <v>31897584</v>
@@ -1480,7 +1723,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="C10">
         <v>31897584</v>
@@ -1510,7 +1753,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="C11">
         <v>31897584</v>
@@ -1540,7 +1783,7 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="C12">
         <v>31897584</v>
@@ -1570,7 +1813,7 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="C13">
         <v>31897584</v>
@@ -1600,7 +1843,7 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="C14">
         <v>31897584</v>
@@ -1630,7 +1873,7 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="C15">
         <v>31897584</v>
@@ -1660,7 +1903,7 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="C16">
         <v>31897584</v>
@@ -1690,7 +1933,7 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="C17">
         <v>31897584</v>
@@ -1720,7 +1963,7 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="C18">
         <v>31897584</v>

--- a/input_data/admin_data/PER/_clean/total-pre-PER.xlsx
+++ b/input_data/admin_data/PER/_clean/total-pre-PER.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="93">
   <si>
     <t>year</t>
   </si>
@@ -342,34 +342,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="H1" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="J1" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
@@ -377,7 +377,7 @@
         <v>2016</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C2">
         <v>30866494</v>
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="C3">
         <v>30866494</v>
@@ -437,7 +437,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C4">
         <v>30866494</v>
@@ -467,7 +467,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="C5">
         <v>30866494</v>
@@ -497,7 +497,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="C6">
         <v>30866494</v>
@@ -527,7 +527,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="C7">
         <v>30866494</v>
@@ -557,7 +557,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>30866494</v>
@@ -587,7 +587,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C9">
         <v>30866494</v>
@@ -617,7 +617,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="C10">
         <v>30866494</v>
@@ -647,7 +647,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="C11">
         <v>30866494</v>
@@ -677,7 +677,7 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="C12">
         <v>30866494</v>
@@ -707,7 +707,7 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="C13">
         <v>30866494</v>
@@ -737,7 +737,7 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="C14">
         <v>30866494</v>
@@ -767,7 +767,7 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="C15">
         <v>30866494</v>
@@ -797,7 +797,7 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="C16">
         <v>30866494</v>
@@ -827,7 +827,7 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="C17">
         <v>30866494</v>
@@ -857,7 +857,7 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="C18">
         <v>30866494</v>
@@ -895,34 +895,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E1" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="G1" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="H1" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="I1" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="J1" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
@@ -930,7 +930,7 @@
         <v>2017</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C2">
         <v>31324636</v>
@@ -960,7 +960,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C3">
         <v>31324636</v>
@@ -990,7 +990,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C4">
         <v>31324636</v>
@@ -1020,7 +1020,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="C5">
         <v>31324636</v>
@@ -1050,7 +1050,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="C6">
         <v>31324636</v>
@@ -1080,7 +1080,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C7">
         <v>31324636</v>
@@ -1110,7 +1110,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>31324636</v>
@@ -1140,7 +1140,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C9">
         <v>31324636</v>
@@ -1170,7 +1170,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="C10">
         <v>31324636</v>
@@ -1200,7 +1200,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C11">
         <v>31324636</v>
@@ -1230,7 +1230,7 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C12">
         <v>31324636</v>
@@ -1260,7 +1260,7 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C13">
         <v>31324636</v>
@@ -1290,7 +1290,7 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="C14">
         <v>31324636</v>
@@ -1320,7 +1320,7 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C15">
         <v>31324636</v>
@@ -1350,7 +1350,7 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C16">
         <v>31324636</v>
@@ -1380,7 +1380,7 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C17">
         <v>31324636</v>
@@ -1410,7 +1410,7 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C18">
         <v>31324636</v>
@@ -1513,7 +1513,7 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="C3">
         <v>31897584</v>
@@ -1543,7 +1543,7 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C4">
         <v>31897584</v>
@@ -1573,7 +1573,7 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C5">
         <v>31897584</v>
@@ -1603,7 +1603,7 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C6">
         <v>31897584</v>
@@ -1633,7 +1633,7 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C7">
         <v>31897584</v>
@@ -1663,7 +1663,7 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>31897584</v>
@@ -1693,7 +1693,7 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C9">
         <v>31897584</v>
@@ -1723,7 +1723,7 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="C10">
         <v>31897584</v>
@@ -1753,7 +1753,7 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C11">
         <v>31897584</v>
@@ -1783,7 +1783,7 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C12">
         <v>31897584</v>
@@ -1813,7 +1813,7 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C13">
         <v>31897584</v>
@@ -1843,7 +1843,7 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C14">
         <v>31897584</v>
@@ -1873,7 +1873,7 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C15">
         <v>31897584</v>
@@ -1903,7 +1903,7 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C16">
         <v>31897584</v>
@@ -1933,7 +1933,7 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C17">
         <v>31897584</v>

--- a/input_data/admin_data/PER/_clean/total-pre-PER.xlsx
+++ b/input_data/admin_data/PER/_clean/total-pre-PER.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="93">
   <si>
     <t>year</t>
   </si>
